--- a/자문지/라이프자산운용_DB 개방형 랩 _2026.4.27.xlsx
+++ b/자문지/라이프자산운용_DB 개방형 랩 _2026.4.27.xlsx
@@ -24,20 +24,20 @@
     <numFmt numFmtId="164" formatCode="0.000_ "/>
     <numFmt numFmtId="165" formatCode="0.0_ "/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="#,##0\ &quot;F&quot;;\-#,##0\ &quot;F&quot;"/>
-    <numFmt numFmtId="169" formatCode="_ &quot;₩&quot;* #,##0_ ;_ &quot;₩&quot;* \-#,##0_ ;_ &quot;₩&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="170" formatCode="#,##0.00000;[Red]\-#,##0.00000"/>
-    <numFmt numFmtId="171" formatCode="&quot;(&quot;#,##0&quot;)&quot;;&quot;(&quot;\-#,##0&quot;)&quot;"/>
-    <numFmt numFmtId="172" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="173" formatCode="0.0_)"/>
-    <numFmt numFmtId="174" formatCode="#,##0.000"/>
-    <numFmt numFmtId="175" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="176" formatCode="0.0"/>
-    <numFmt numFmtId="177" formatCode="0_%_);\(0\)_%;0_%_);@_%_)"/>
-    <numFmt numFmtId="178" formatCode="&quot;₩&quot;#,##0.00;[Red]&quot;₩&quot;\-#,##0.00"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="180" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="168" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="#,##0\ &quot;F&quot;;\-#,##0\ &quot;F&quot;"/>
+    <numFmt numFmtId="170" formatCode="_ &quot;₩&quot;* #,##0_ ;_ &quot;₩&quot;* \-#,##0_ ;_ &quot;₩&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="171" formatCode="#,##0.00000;[Red]\-#,##0.00000"/>
+    <numFmt numFmtId="172" formatCode="&quot;(&quot;#,##0&quot;)&quot;;&quot;(&quot;\-#,##0&quot;)&quot;"/>
+    <numFmt numFmtId="173" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="174" formatCode="0.0_)"/>
+    <numFmt numFmtId="175" formatCode="#,##0.000"/>
+    <numFmt numFmtId="176" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="177" formatCode="0.0"/>
+    <numFmt numFmtId="178" formatCode="0_%_);\(0\)_%;0_%_);@_%_)"/>
+    <numFmt numFmtId="179" formatCode="&quot;₩&quot;#,##0.00;[Red]&quot;₩&quot;\-#,##0.00"/>
+    <numFmt numFmtId="180" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="107">
     <font>
@@ -1217,7 +1217,7 @@
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="56" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="56" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="56" fillId="0" borderId="0"/>
     <xf numFmtId="39" fontId="68" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1225,7 +1225,7 @@
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="57" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="57" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0"/>
@@ -1235,22 +1235,22 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0"/>
-    <xf numFmtId="169" fontId="52" fillId="0" borderId="0"/>
+    <xf numFmtId="170" fontId="52" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0"/>
     <xf numFmtId="4" fontId="75" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="56" fillId="0" borderId="0"/>
-    <xf numFmtId="170" fontId="56" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="56" fillId="0" borderId="0"/>
+    <xf numFmtId="171" fontId="56" fillId="0" borderId="0"/>
     <xf numFmtId="14" fontId="70" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="171" fontId="52" fillId="0" borderId="0"/>
     <xf numFmtId="172" fontId="52" fillId="0" borderId="0"/>
     <xf numFmtId="173" fontId="52" fillId="0" borderId="0"/>
     <xf numFmtId="174" fontId="52" fillId="0" borderId="0"/>
+    <xf numFmtId="175" fontId="52" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="76" fillId="2" borderId="0"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1271,7 +1271,7 @@
     <xf numFmtId="10" fontId="76" fillId="2" borderId="1"/>
     <xf numFmtId="10" fontId="82" fillId="4" borderId="7"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="4"/>
-    <xf numFmtId="175" fontId="84" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="84" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="8"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0"/>
@@ -1280,7 +1280,7 @@
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="177" fontId="56" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="3" applyAlignment="1">
@@ -1308,7 +1308,7 @@
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="92" fillId="0" borderId="9" applyAlignment="1">
+    <xf numFmtId="178" fontId="92" fillId="0" borderId="9" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="9" applyAlignment="1" applyProtection="1">
@@ -1338,7 +1338,7 @@
     </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0"/>
-    <xf numFmtId="178" fontId="56" fillId="0" borderId="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="56" fillId="0" borderId="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
@@ -1529,7 +1529,7 @@
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0"/>
-    <xf numFmtId="179" fontId="52" fillId="0" borderId="0"/>
+    <xf numFmtId="180" fontId="52" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2500,7 +2500,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2574,7 +2574,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="180" fontId="103" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="103" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="103" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
@@ -2584,6 +2584,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="101" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="103" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4383,7 +4386,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="22" t="inlineStr">
         <is>
-          <t>DB금융투자 라이프 자문형 랩 현황</t>
+          <t>DB증권 라이프 자문형 랩 현황</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4403,7 @@
     </row>
     <row r="4" ht="14.25" customHeight="1" s="24">
       <c r="A4" s="1" t="n"/>
-      <c r="B4" s="25">
+      <c r="B4" s="29">
         <f>TODAY()</f>
         <v/>
       </c>

--- a/자문지/라이프자산운용_DB 개방형 랩 _2026.4.27.xlsx
+++ b/자문지/라이프자산운용_DB 개방형 랩 _2026.4.27.xlsx
@@ -4386,7 +4386,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="22" t="inlineStr">
         <is>
-          <t>DB증권 라이프 자문형 랩 현황</t>
+          <t>DB증권 라이프 개방형 랩 현황</t>
         </is>
       </c>
     </row>
